--- a/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
@@ -539,10 +539,10 @@
         <v>3.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="H10" t="n">
-        <v>23.4</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>27.73</v>
+        <v>25.33</v>
       </c>
     </row>
     <row r="15">
@@ -802,10 +802,10 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>36.4</v>
+        <v>34</v>
       </c>
       <c r="H24" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="25">
@@ -821,7 +821,7 @@
       </c>
       <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>36.76</v>
+        <v>34.34</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos continuos de concreto y microcemento</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-06-030.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revestimiento continuo de microcemento sobre piso existente o contrapiso, aplicado en capas con malla de refuerzo y sellado con varias manos de barniz de protección. Permite renovar un piso sin demolerlo y sin apenas ganar cota, lo que en reforma resuelve el problema de los umbrales y las puertas. Es muy sensible al soporte: cualquier fisura o movimiento se refleja en el acabado. Incluye la comprobación y estabilización del soporte, la imprimación, la capa base con malla, las capas de acabado con la textura elegida, el lijado entre capas y las manos de sellador de alto tránsito. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
+          <t xml:space="preserve">Revestimiento continuo de microcemento sobre piso existente o afirmado, aplicado en capas con malla de refuerzo y sellado con varias manos de barniz de protección. Permite renovar un piso sin demolerlo y sin apenas ganar cota, lo que en reforma resuelve el problema de los umbrales y las puertas. Es muy sensible al soporte: cualquier fisura o movimiento se refleja en el acabado. Incluye la comprobación y estabilización del soporte, la imprimación, la capa base con malla, las capas de acabado con la textura elegida, el lijado entre capas y las manos de sellador de alto tránsito. Medido en superficie realmente ejecutada, descontando huecos mayores de 1 m².
 </t>
         </is>
       </c>
@@ -732,7 +732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F20" t="n">
